--- a/questionnaire_templates/048_monat_hair_consultation_quiz--questionnaire_templates.xlsx
+++ b/questionnaire_templates/048_monat_hair_consultation_quiz--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'curly',_'label':_'curly'}</t>
+          <t>curly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'curly', 'label': 'curly'}</t>
+          <t>curly</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'wavy',_'label':_'wavy'}</t>
+          <t>wavy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'wavy', 'label': 'wavy'}</t>
+          <t>wavy</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'straight',_'label':_'straight'}</t>
+          <t>straight</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'straight', 'label': 'straight'}</t>
+          <t>straight</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'blonde'}</t>
+          <t>blonde</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'blonde'}</t>
+          <t>blonde</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'brunette'}</t>
+          <t>brunette</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'brunette'}</t>
+          <t>brunette</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'redhead'}</t>
+          <t>redhead</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'redhead'}</t>
+          <t>redhead</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'gray'}</t>
+          <t>gray</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'gray'}</t>
+          <t>gray</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'platinum'}</t>
+          <t>platinum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'platinum'}</t>
+          <t>platinum</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monat_tone'}</t>
+          <t>monat_tone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'monat_tone'}</t>
+          <t>monat tone</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'monat_shine'}</t>
+          <t>monat_shine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'monat_shine'}</t>
+          <t>monat shine</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monat_hair'}</t>
+          <t>monat_hair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'monat_hair'}</t>
+          <t>monat hair</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'monat_pro'}</t>
+          <t>monat_pro</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'monat_pro'}</t>
+          <t>monat pro</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'monat_fusion'}</t>
+          <t>monat_fusion</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'monat_fusion'}</t>
+          <t>monat fusion</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'monat_dry_shampoo'}</t>
+          <t>monat_dry_shampoo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'monat_dry_shampoo'}</t>
+          <t>monat dry shampoo</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'natural'}</t>
+          <t>natural</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'natural'}</t>
+          <t>natural</t>
         </is>
       </c>
     </row>
@@ -1471,114 +1471,114 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'color'}</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'color'}</t>
+          <t>color</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hair_type_1_choices</t>
+          <t>hair_color_1_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'color'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'color'}</t>
+          <t>black</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hair_type_1_choices</t>
+          <t>hair_color_1_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'color'}</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'color'}</t>
+          <t>brown</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hair_color_1_choices</t>
+          <t>natural_ingredients_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'black'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'black'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hair_color_1_choices</t>
+          <t>natural_ingredients_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'brown'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'brown'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>natural_ingredients_choices</t>
+          <t>hair_growth_rate_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>slow</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>natural_ingredients_choices</t>
+          <t>hair_growth_rate_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -1590,505 +1590,386 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'slow'}</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'slow'}</t>
+          <t>fast</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hair_growth_rate_choices</t>
+          <t>previous_products_1_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>monat</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medium'}</t>
+          <t>monat</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hair_growth_rate_choices</t>
+          <t>previous_products_1_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fast'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'fast'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>previous_products_1_choices</t>
+          <t>monat_products_1_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monat'}</t>
+          <t>monat</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'monat'}</t>
+          <t>monat</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>previous_products_1_choices</t>
+          <t>monat_products_1_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'monat'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'monat'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>previous_products_1_choices</t>
+          <t>hair_problems_1_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monat'}</t>
+          <t>frizzy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'monat'}</t>
+          <t>frizzy</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>previous_products_1_choices</t>
+          <t>hair_problems_1_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'monat'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'monat'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>monat_products_1_choices</t>
+          <t>have_used_monat_fusion_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monat'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'monat'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>monat_products_1_choices</t>
+          <t>have_used_monat_fusion_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'monat'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'monat'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>monat_products_1_choices</t>
+          <t>hair_problems_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monat'}</t>
+          <t>frizzy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'monat'}</t>
+          <t>frizzy</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hair_problems_1_choices</t>
+          <t>hair_problems_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'frizzy'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'frizzy'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hair_problems_1_choices</t>
+          <t>previous_monat_products_1_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'frizzy'}</t>
+          <t>monat</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'frizzy'}</t>
+          <t>monat</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>hair_problems_1_choices</t>
+          <t>previous_monat_products_1_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'frizzy'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'frizzy'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>have_used_monat_fusion_choices</t>
+          <t>have_shared_monat_fusion_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>have_used_monat_fusion_choices</t>
+          <t>have_shared_monat_fusion_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hair_problems_2_choices</t>
+          <t>previous_monat_products_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'frizzy'}</t>
+          <t>monat</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'frizzy'}</t>
+          <t>monat</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hair_problems_2_choices</t>
+          <t>previous_monat_products_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'frizzy'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'frizzy'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>previous_monat_products_1_choices</t>
+          <t>monat_products_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monat'}</t>
+          <t>monat</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'monat'}</t>
+          <t>monat</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>previous_monat_products_1_choices</t>
+          <t>monat_products_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'monat'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'monat'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>previous_monat_products_1_choices</t>
+          <t>previous_monat_products_3_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monat'}</t>
+          <t>monat</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'monat'}</t>
+          <t>monat</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>have_shared_monat_fusion_choices</t>
+          <t>previous_monat_products_3_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>have_shared_monat_fusion_choices</t>
+          <t>have_used_monat_hair_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>previous_monat_products_2_choices</t>
+          <t>have_used_monat_hair_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monat'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'monat'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>previous_monat_products_2_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'monat'}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'monat'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>monat_products_2_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'monat'}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'monat'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>monat_products_2_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'monat'}</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'monat'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>previous_monat_products_3_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'monat'}</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'monat'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>previous_monat_products_3_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'monat'}</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'monat'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>have_used_monat_hair_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_true}</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>have_used_monat_hair_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_false}</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
